--- a/pontos_corridos/datasets_pontos_corridos/times.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/times.xlsx
@@ -487,7 +487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GE Bebum</t>
+          <t>GE Xavanchesteer</t>
         </is>
       </c>
     </row>
